--- a/public/templates/usa-upload-template.xlsx
+++ b/public/templates/usa-upload-template.xlsx
@@ -4,7 +4,6 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Holdings" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -415,389 +414,232 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Symbol</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Cost Basis</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Market Price</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Market Value</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Unrealised P&amp;L</v>
-      </c>
-      <c r="H1" t="str">
-        <v>ISIN</v>
-      </c>
-      <c r="I1" t="str">
-        <v>CUSIP</v>
-      </c>
-      <c r="J1" t="str">
-        <v>SEDOL</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Exchange</v>
+        <v>USA Brokerage Upload Template</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AAPL</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Apple Inc.</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2">
-        <v>15000</v>
-      </c>
-      <c r="E2">
-        <v>195.5</v>
-      </c>
-      <c r="F2">
-        <v>19550</v>
-      </c>
-      <c r="G2">
-        <v>4550</v>
-      </c>
-      <c r="H2" t="str">
-        <v>US0378331005</v>
-      </c>
-      <c r="I2" t="str">
-        <v>037833100</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v>NASDAQ</v>
+        <v>Fill in your holdings below. Symbol and Quantity are required. Delete the sample rows or replace them.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MSFT</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Microsoft Corporation</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>18000</v>
-      </c>
-      <c r="E3">
-        <v>420.25</v>
-      </c>
-      <c r="F3">
-        <v>21012.5</v>
-      </c>
-      <c r="G3">
-        <v>3012.5</v>
-      </c>
-      <c r="H3" t="str">
-        <v>US5949181045</v>
-      </c>
-      <c r="I3" t="str">
-        <v>594918104</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>NASDAQ</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>GOOGL</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Alphabet Inc. Class A</v>
-      </c>
-      <c r="C4">
-        <v>75</v>
-      </c>
-      <c r="D4">
-        <v>10500</v>
-      </c>
-      <c r="E4">
-        <v>175.8</v>
-      </c>
-      <c r="F4">
-        <v>13185</v>
-      </c>
-      <c r="G4">
-        <v>2685</v>
-      </c>
-      <c r="H4" t="str">
-        <v>US02079K3059</v>
-      </c>
-      <c r="I4" t="str">
-        <v>02079K305</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>NASDAQ</v>
+        <v>Symbol format: 1-5 letter tickers (e.g. AAPL, MSFT, BRK.B). Amounts are in USD.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BRK.B</v>
+        <v>Symbol</v>
       </c>
       <c r="B5" t="str">
-        <v>Berkshire Hathaway Inc. Class B</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>9000</v>
-      </c>
-      <c r="E5">
-        <v>410</v>
-      </c>
-      <c r="F5">
-        <v>10250</v>
-      </c>
-      <c r="G5">
-        <v>1250</v>
+        <v>Name</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Cost Basis</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Market Price</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Market Value</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Unrealised P&amp;L</v>
       </c>
       <c r="H5" t="str">
-        <v>US0846707026</v>
+        <v>ISIN</v>
       </c>
       <c r="I5" t="str">
-        <v>084670702</v>
+        <v>CUSIP</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>SEDOL</v>
       </c>
       <c r="K5" t="str">
-        <v>NYSE</v>
+        <v>Exchange</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VOO</v>
+        <v>AAPL</v>
       </c>
       <c r="B6" t="str">
-        <v>Vanguard S&amp;P 500 ETF</v>
+        <v>Apple Inc.</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E6">
-        <v>485.75</v>
+        <v>195.5</v>
       </c>
       <c r="F6">
-        <v>14572.5</v>
+        <v>19550</v>
       </c>
       <c r="G6">
-        <v>2572.5</v>
+        <v>4550</v>
       </c>
       <c r="H6" t="str">
-        <v>US9229083632</v>
+        <v>US0378331005</v>
       </c>
       <c r="I6" t="str">
-        <v>922908363</v>
+        <v>037833100</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v>NASDAQ</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>MSFT</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Microsoft Corporation</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>18000</v>
+      </c>
+      <c r="E7">
+        <v>420.25</v>
+      </c>
+      <c r="F7">
+        <v>21012.5</v>
+      </c>
+      <c r="G7">
+        <v>3012.5</v>
+      </c>
+      <c r="H7" t="str">
+        <v>US5949181045</v>
+      </c>
+      <c r="I7" t="str">
+        <v>594918104</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>NASDAQ</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GOOGL</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Alphabet Inc. Class A</v>
+      </c>
+      <c r="C8">
+        <v>75</v>
+      </c>
+      <c r="D8">
+        <v>10500</v>
+      </c>
+      <c r="E8">
+        <v>175.8</v>
+      </c>
+      <c r="F8">
+        <v>13185</v>
+      </c>
+      <c r="G8">
+        <v>2685</v>
+      </c>
+      <c r="H8" t="str">
+        <v>US02079K3059</v>
+      </c>
+      <c r="I8" t="str">
+        <v>02079K305</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>NASDAQ</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BRK.B</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Berkshire Hathaway Inc. Class B</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>9000</v>
+      </c>
+      <c r="E9">
+        <v>410</v>
+      </c>
+      <c r="F9">
+        <v>10250</v>
+      </c>
+      <c r="G9">
+        <v>1250</v>
+      </c>
+      <c r="H9" t="str">
+        <v>US0846707026</v>
+      </c>
+      <c r="I9" t="str">
+        <v>084670702</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>NYSE</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>VOO</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Vanguard S&amp;P 500 ETF</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>12000</v>
+      </c>
+      <c r="E10">
+        <v>485.75</v>
+      </c>
+      <c r="F10">
+        <v>14572.5</v>
+      </c>
+      <c r="G10">
+        <v>2572.5</v>
+      </c>
+      <c r="H10" t="str">
+        <v>US9229083632</v>
+      </c>
+      <c r="I10" t="str">
+        <v>922908363</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v>NYSE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="72.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>USA — Brokerage Upload Template</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>How to use</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1. Fill the Holdings sheet with your positions (Symbol and Quantity are required).</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2. Save as .xlsx and upload via Portfolio → Public Markets → USA → Import Brokerage Reports.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3. Select the entity that owns these holdings before uploading.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Column guide</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Symbol</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Ticker code — 1–5 letter tickers (e.g. AAPL, MSFT, BRK.B)</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Security name (optional)</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Number of shares/units held (required)</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Cost Basis</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Total purchase cost for the position (USD)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Market Price</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Latest price per share (USD)</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Market Value</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Current position value (USD)</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Unrealised P&amp;L</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Gain or loss vs cost basis</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>ISIN / CUSIP / SEDOL</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Security identifiers when available</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Exchange</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Listing exchange (optional; defaults to NYSE/NASDAQ for USA)</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Accepted file formats</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Excel (.xlsx, .xls) and CSV</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>• Delete the sample rows before uploading your real portfolio, or replace them.</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>• Broker exports from Schwab, Interactive Brokers, Fidelity, etc. are also supported.</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>• Use class suffixes for share classes (e.g. BRK.B, GOOGL).</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>• CUSIP is optional but helps identify securities when symbols differ by broker.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/usa-upload-template.xlsx
+++ b/public/templates/usa-upload-template.xlsx
@@ -1,47 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Holdings" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Holdings" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+  <si>
+    <t>USA Brokerage Upload Template</t>
+  </si>
+  <si>
+    <t>Fill in your holdings below. Symbol and Quantity are required. Delete the sample rows or replace them.</t>
+  </si>
+  <si>
+    <t>Symbol format: 1-5 letter tickers (e.g. AAPL, MSFT, BRK.B). Amounts are in USD.</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Cost Basis</t>
+  </si>
+  <si>
+    <t>Market Price</t>
+  </si>
+  <si>
+    <t>Market Value</t>
+  </si>
+  <si>
+    <t>Unrealised P&amp;L</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>CUSIP</t>
+  </si>
+  <si>
+    <t>SEDOL</t>
+  </si>
+  <si>
+    <t>Exchange</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apple Inc.</t>
+  </si>
+  <si>
+    <t>US0378331005</t>
+  </si>
+  <si>
+    <t>037833100</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NASDAQ</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation</t>
+  </si>
+  <si>
+    <t>US5949181045</t>
+  </si>
+  <si>
+    <t>594918104</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. Class A</t>
+  </si>
+  <si>
+    <t>US02079K3059</t>
+  </si>
+  <si>
+    <t>02079K305</t>
+  </si>
+  <si>
+    <t>BRK.B</t>
+  </si>
+  <si>
+    <t>Berkshire Hathaway Inc. Class B</t>
+  </si>
+  <si>
+    <t>US0846707026</t>
+  </si>
+  <si>
+    <t>084670702</t>
+  </si>
+  <si>
+    <t>NYSE</t>
+  </si>
+  <si>
+    <t>VOO</t>
+  </si>
+  <si>
+    <t>Vanguard S&amp;P 500 ETF</t>
+  </si>
+  <si>
+    <t>US9229083632</t>
+  </si>
+  <si>
+    <t>922908363</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,13 +158,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,78 +497,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K10"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>USA Brokerage Upload Template</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Fill in your holdings below. Symbol and Quantity are required. Delete the sample rows or replace them.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Symbol format: 1-5 letter tickers (e.g. AAPL, MSFT, BRK.B). Amounts are in USD.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Symbol</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Cost Basis</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Market Price</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Market Value</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Unrealised P&amp;L</v>
-      </c>
-      <c r="H5" t="str">
-        <v>ISIN</v>
-      </c>
-      <c r="I5" t="str">
-        <v>CUSIP</v>
-      </c>
-      <c r="J5" t="str">
-        <v>SEDOL</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Exchange</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>AAPL</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Apple Inc.</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -484,25 +573,25 @@
       <c r="G6">
         <v>4550</v>
       </c>
-      <c r="H6" t="str">
-        <v>US0378331005</v>
-      </c>
-      <c r="I6" t="str">
-        <v>037833100</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v>NASDAQ</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>MSFT</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Microsoft Corporation</v>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -519,25 +608,25 @@
       <c r="G7">
         <v>3012.5</v>
       </c>
-      <c r="H7" t="str">
-        <v>US5949181045</v>
-      </c>
-      <c r="I7" t="str">
-        <v>594918104</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>NASDAQ</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>GOOGL</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Alphabet Inc. Class A</v>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
       </c>
       <c r="C8">
         <v>75</v>
@@ -554,25 +643,25 @@
       <c r="G8">
         <v>2685</v>
       </c>
-      <c r="H8" t="str">
-        <v>US02079K3059</v>
-      </c>
-      <c r="I8" t="str">
-        <v>02079K305</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v>NASDAQ</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>BRK.B</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Berkshire Hathaway Inc. Class B</v>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
       </c>
       <c r="C9">
         <v>25</v>
@@ -589,25 +678,25 @@
       <c r="G9">
         <v>1250</v>
       </c>
-      <c r="H9" t="str">
-        <v>US0846707026</v>
-      </c>
-      <c r="I9" t="str">
-        <v>084670702</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v>NYSE</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>VOO</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Vanguard S&amp;P 500 ETF</v>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
       </c>
       <c r="C10">
         <v>30</v>
@@ -624,22 +713,21 @@
       <c r="G10">
         <v>2572.5</v>
       </c>
-      <c r="H10" t="str">
-        <v>US9229083632</v>
-      </c>
-      <c r="I10" t="str">
-        <v>922908363</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v>NYSE</v>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>